--- a/jira_export_2026-07-30.xlsx
+++ b/jira_export_2026-07-30.xlsx
@@ -723,7 +723,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>64,023 €</t>
+          <t>63,159 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -737,7 +737,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -763,14 +763,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>23,404 €</t>
+          <t>23,600 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>40,619 €</t>
+          <t>39,559 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -818,7 +818,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>576 h</t>
+          <t>577 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -832,7 +832,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="8" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -903,7 +903,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2189,7 +2189,7 @@
         </is>
       </c>
       <c r="N20" s="15" t="n">
-        <v>0</v>
+        <v>1660</v>
       </c>
       <c r="O20" s="15" t="n">
         <v>2075</v>
@@ -2400,10 +2400,10 @@
         <v>1296</v>
       </c>
       <c r="O23" s="12" t="n">
-        <v>2376</v>
+        <v>2448</v>
       </c>
       <c r="P23" s="12" t="n">
-        <v>153.29</v>
+        <v>157.94</v>
       </c>
     </row>
     <row r="24">
@@ -2895,11 +2895,11 @@
       <c r="N30" s="15" t="n">
         <v>353.5</v>
       </c>
-      <c r="O30" s="15" t="n">
-        <v>1060.5</v>
+      <c r="O30" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P30" s="15" t="n">
-        <v>2121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -3320,10 +3320,10 @@
         <v>1242.9</v>
       </c>
       <c r="O36" s="16" t="n">
-        <v>870.03</v>
+        <v>994.3200000000001</v>
       </c>
       <c r="P36" s="15" t="n">
-        <v>79.09</v>
+        <v>90.39</v>
       </c>
     </row>
     <row r="37">
@@ -12700,7 +12700,7 @@
         <v>27</v>
       </c>
       <c r="K169" s="11" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="L169" s="11" t="inlineStr">
         <is>
@@ -13939,13 +13939,13 @@
       <c r="L190" s="17" t="inlineStr"/>
       <c r="M190" s="17" t="inlineStr"/>
       <c r="N190" s="18" t="n">
-        <v>62442.1</v>
+        <v>64102.1</v>
       </c>
       <c r="O190" s="18" t="n">
-        <v>64023.09500000001</v>
+        <v>63158.88500000001</v>
       </c>
       <c r="P190" s="18" t="n">
-        <v>182.66</v>
+        <v>179.81</v>
       </c>
     </row>
   </sheetData>
@@ -15163,7 +15163,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>199.25</v>
+        <v>200</v>
       </c>
       <c r="C5" s="14" t="n">
         <v>36</v>
@@ -15172,7 +15172,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>239.25</v>
+        <v>240</v>
       </c>
       <c r="F5" s="14" t="n">
         <v>68.5</v>
@@ -15182,7 +15182,7 @@
       </c>
       <c r="H5" s="21" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
     </row>
@@ -15224,7 +15224,7 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>132.58</v>
+        <v>133.08</v>
       </c>
     </row>
   </sheetData>
@@ -15309,10 +15309,10 @@
         </is>
       </c>
       <c r="B5" s="24" t="n">
-        <v>387310</v>
+        <v>386693</v>
       </c>
       <c r="C5" s="24" t="n">
-        <v>129194</v>
+        <v>128576</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>258116</v>
@@ -15334,10 +15334,10 @@
         </is>
       </c>
       <c r="B6" s="25" t="n">
-        <v>175551</v>
+        <v>177055</v>
       </c>
       <c r="C6" s="25" t="n">
-        <v>70156</v>
+        <v>71660</v>
       </c>
       <c r="D6" s="25" t="n">
         <v>105395</v>
@@ -15359,10 +15359,10 @@
         </is>
       </c>
       <c r="B7" s="26" t="n">
-        <v>211759</v>
+        <v>209638</v>
       </c>
       <c r="C7" s="26" t="n">
-        <v>59037</v>
+        <v>56916</v>
       </c>
       <c r="D7" s="26" t="n">
         <v>152722</v>
@@ -15388,7 +15388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15412,7 +15412,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 20 commande(s)</t>
+          <t>Épics créées ce mois — 21 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15512,22 +15512,22 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -15547,22 +15547,22 @@
       </c>
       <c r="H6" s="11" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I6" s="26" t="n">
-        <v>0</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="C7" s="14" t="inlineStr">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -15582,7 +15582,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -15592,32 +15592,32 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="I7" s="25" t="n">
-        <v>2146.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="F8" s="11" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G8" s="11" t="inlineStr">
@@ -15637,32 +15637,32 @@
       </c>
       <c r="H8" s="11" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="I8" s="26" t="n">
-        <v>4475</v>
+        <v>2146.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -15682,32 +15682,32 @@
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I9" s="25" t="n">
-        <v>5585</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -15727,11 +15727,11 @@
       </c>
       <c r="H10" s="11" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="I10" s="26" t="n">
-        <v>1050</v>
+        <v>5585</v>
       </c>
     </row>
     <row r="11">
@@ -16142,22 +16142,22 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34852</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="D20" s="11" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E20" s="11" t="inlineStr">
@@ -16177,32 +16177,32 @@
       </c>
       <c r="H20" s="11" t="inlineStr">
         <is>
-          <t>00177232</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="I20" s="26" t="n">
-        <v>0</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34861</t>
         </is>
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34857</t>
         </is>
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -16222,11 +16222,11 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00177271</t>
         </is>
       </c>
       <c r="I21" s="25" t="n">
-        <v>2800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="22">
@@ -16265,22 +16265,22 @@
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34852</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34848</t>
         </is>
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -16300,83 +16300,107 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00177232</t>
         </is>
       </c>
       <c r="I23" s="25" t="n">
-        <v>4300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
+          <t>PDMDEP-34722</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="inlineStr">
+        <is>
+          <t>PDMDEP-34718</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>24/07/2026</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>VILLE DE VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G24" s="11" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H24" s="11" t="inlineStr">
+        <is>
+          <t>00176875</t>
+        </is>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="14" t="inlineStr">
+        <is>
           <t>PDMDEP-34654</t>
         </is>
       </c>
-      <c r="B24" s="11" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>PDMDEP-34650</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C25" s="14" t="inlineStr">
         <is>
           <t>21/07/2026</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E25" s="14" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F25" s="14" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G25" s="14" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>00176582</t>
         </is>
       </c>
-      <c r="I24" s="26" t="n">
+      <c r="I25" s="25" t="n">
         <v>495</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="n"/>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="17" t="n"/>
-      <c r="H25" s="17" t="inlineStr">
-        <is>
-          <t>20 commande(s)</t>
-        </is>
-      </c>
-      <c r="I25" s="24" t="n">
-        <v>38784</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="17" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B26" s="17" t="n"/>
@@ -16387,17 +16411,17 @@
       <c r="G26" s="17" t="n"/>
       <c r="H26" s="17" t="inlineStr">
         <is>
-          <t>5 commande(s)</t>
+          <t>21 commande(s)</t>
         </is>
       </c>
       <c r="I26" s="24" t="n">
-        <v>8095</v>
+        <v>40484</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B27" s="17" t="n"/>
@@ -16408,10 +16432,31 @@
       <c r="G27" s="17" t="n"/>
       <c r="H27" s="17" t="inlineStr">
         <is>
+          <t>6 commande(s)</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="n">
+        <v>9795</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="17" t="n"/>
+      <c r="H28" s="17" t="inlineStr">
+        <is>
           <t>15 commande(s)</t>
         </is>
       </c>
-      <c r="I27" s="24" t="n">
+      <c r="I28" s="24" t="n">
         <v>30689</v>
       </c>
     </row>

--- a/jira_export_2026-07-30.xlsx
+++ b/jira_export_2026-07-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>66,685 €</t>
+          <t>67,702 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>43,085 €</t>
+          <t>44,102 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>580 h</t>
+          <t>581 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>75.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P192"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -961,7 +961,7 @@
     <col width="17" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
-    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
     <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
@@ -2409,7 +2409,7 @@
         <v>2127.2</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>2552.64</v>
+        <v>3509.88</v>
       </c>
       <c r="P23" s="13" t="n">
         <v>0</v>
@@ -3121,10 +3121,10 @@
         <v>280</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>1680</v>
+        <v>1740</v>
       </c>
       <c r="P33" s="13" t="n">
-        <v>3360</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="34">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="G36" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Prestation offerte</t>
         </is>
       </c>
       <c r="H36" s="15" t="inlineStr">
@@ -3398,7 +3398,7 @@
         </is>
       </c>
       <c r="N37" s="13" t="n">
-        <v>1242.9</v>
+        <v>1000</v>
       </c>
       <c r="O37" s="17" t="n">
         <v>994.3200000000001</v>
@@ -13628,18 +13628,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1310</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13656,14 +13656,14 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L184" s="15" t="inlineStr"/>
       <c r="M184" s="15" t="inlineStr"/>
@@ -13680,18 +13680,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13702,36 +13702,28 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L185" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M185" s="12" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L185" s="12" t="inlineStr"/>
+      <c r="M185" s="12" t="inlineStr"/>
       <c r="N185" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O185" s="13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P185" s="13" t="n">
         <v>0</v>
@@ -13740,18 +13732,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1310</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13762,56 +13754,48 @@
       </c>
       <c r="G186" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="L186" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M186" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L186" s="15" t="inlineStr"/>
+      <c r="M186" s="15" t="inlineStr"/>
       <c r="N186" s="16" t="n">
-        <v>510.6</v>
+        <v>0</v>
       </c>
       <c r="O186" s="16" t="n">
-        <v>680.8</v>
+        <v>0</v>
       </c>
       <c r="P186" s="16" t="n">
-        <v>389.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13828,30 +13812,30 @@
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33167</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M187" s="12" t="inlineStr">
         <is>
-          <t>00165437</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N187" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O187" s="13" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="P187" s="13" t="n">
         <v>0</v>
@@ -13860,18 +13844,18 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13882,48 +13866,56 @@
       </c>
       <c r="G188" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L188" s="15" t="inlineStr"/>
-      <c r="M188" s="15" t="inlineStr"/>
+        <v>1.75</v>
+      </c>
+      <c r="L188" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M188" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
       <c r="N188" s="16" t="n">
-        <v>0</v>
+        <v>510.6</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>0</v>
+        <v>680.8</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>0</v>
+        <v>389.03</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13934,28 +13926,36 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L189" s="12" t="inlineStr"/>
-      <c r="M189" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33167</t>
+        </is>
+      </c>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>00165437</t>
+        </is>
+      </c>
       <c r="N189" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O189" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P189" s="13" t="n">
         <v>0</v>
@@ -13964,18 +13964,18 @@
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13992,11 +13992,11 @@
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K190" s="15" t="n">
         <v>0.5</v>
@@ -14016,18 +14016,18 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -14044,14 +14044,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -14066,31 +14066,135 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="18" t="inlineStr">
+      <c r="A192" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1021</t>
+        </is>
+      </c>
+      <c r="B192" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="C192" s="15" t="inlineStr"/>
+      <c r="D192" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MELESSE</t>
+        </is>
+      </c>
+      <c r="E192" s="15" t="inlineStr"/>
+      <c r="F192" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G192" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H192" s="15" t="inlineStr"/>
+      <c r="I192" s="15" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="J192" s="15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K192" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L192" s="15" t="inlineStr"/>
+      <c r="M192" s="15" t="inlineStr"/>
+      <c r="N192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr"/>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr"/>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H193" s="12" t="inlineStr"/>
+      <c r="I193" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J193" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K193" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L193" s="12" t="inlineStr"/>
+      <c r="M193" s="12" t="inlineStr"/>
+      <c r="N193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B192" s="18" t="inlineStr"/>
-      <c r="C192" s="18" t="inlineStr"/>
-      <c r="D192" s="18" t="inlineStr"/>
-      <c r="E192" s="18" t="inlineStr"/>
-      <c r="F192" s="18" t="inlineStr"/>
-      <c r="G192" s="18" t="inlineStr"/>
-      <c r="H192" s="18" t="inlineStr"/>
-      <c r="I192" s="18" t="inlineStr"/>
-      <c r="J192" s="18" t="inlineStr"/>
-      <c r="K192" s="18" t="inlineStr"/>
-      <c r="L192" s="18" t="inlineStr"/>
-      <c r="M192" s="18" t="inlineStr"/>
-      <c r="N192" s="19" t="n">
-        <v>64102.10000000001</v>
-      </c>
-      <c r="O192" s="19" t="n">
-        <v>66685.02500000001</v>
-      </c>
-      <c r="P192" s="19" t="n">
-        <v>187.97</v>
+      <c r="B194" s="18" t="inlineStr"/>
+      <c r="C194" s="18" t="inlineStr"/>
+      <c r="D194" s="18" t="inlineStr"/>
+      <c r="E194" s="18" t="inlineStr"/>
+      <c r="F194" s="18" t="inlineStr"/>
+      <c r="G194" s="18" t="inlineStr"/>
+      <c r="H194" s="18" t="inlineStr"/>
+      <c r="I194" s="18" t="inlineStr"/>
+      <c r="J194" s="18" t="inlineStr"/>
+      <c r="K194" s="18" t="inlineStr"/>
+      <c r="L194" s="18" t="inlineStr"/>
+      <c r="M194" s="18" t="inlineStr"/>
+      <c r="N194" s="19" t="n">
+        <v>63859.2</v>
+      </c>
+      <c r="O194" s="19" t="n">
+        <v>67702.265</v>
+      </c>
+      <c r="P194" s="19" t="n">
+        <v>190.57</v>
       </c>
     </row>
   </sheetData>
@@ -14283,6 +14387,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId185"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15316,20 +15422,20 @@
         <v>36.25</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>5.25</v>
+        <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>244.75</v>
+        <v>245.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>68.5</v>
+        <v>69</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>455.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.8%</t>
         </is>
       </c>
     </row>
@@ -15340,13 +15446,13 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>101.25</v>
+        <v>101</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>109.5</v>
@@ -15456,10 +15562,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>383167</v>
+        <v>382150</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>132886</v>
+        <v>131869</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>250280</v>
@@ -15506,10 +15612,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>206112</v>
+        <v>205095</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>64026</v>
+        <v>63009</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>142086</v>

--- a/jira_export_2026-07-30.xlsx
+++ b/jira_export_2026-07-30.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>67,702 €</t>
+          <t>69,262 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>72.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>23,600 €</t>
+          <t>25,160 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>581 h</t>
+          <t>584 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>75.6%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P194"/>
+  <dimension ref="A1:P193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -5249,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L63" s="12" t="inlineStr">
         <is>
@@ -5265,10 +5265,10 @@
         <v>625</v>
       </c>
       <c r="O63" s="17" t="n">
-        <v>0</v>
+        <v>135</v>
       </c>
       <c r="P63" s="13" t="n">
-        <v>0</v>
+        <v>77.14</v>
       </c>
     </row>
     <row r="64">
@@ -5321,7 +5321,7 @@
         <v>2</v>
       </c>
       <c r="K64" s="15" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="L64" s="15" t="inlineStr">
         <is>
@@ -5337,10 +5337,10 @@
         <v>600</v>
       </c>
       <c r="O64" s="17" t="n">
-        <v>224</v>
+        <v>304</v>
       </c>
       <c r="P64" s="16" t="n">
-        <v>179.2</v>
+        <v>173.71</v>
       </c>
     </row>
     <row r="65">
@@ -5850,32 +5850,32 @@
     <row r="72">
       <c r="A72" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32831</t>
+          <t>PDMDEP-32768</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE PANTIN] - Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE PANTIN</t>
+          <t>VILLE DE REIMS</t>
         </is>
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>Commande 2 interfaces Ciril Finance pour GEODP TLPE ET VOIRIE</t>
+          <t>MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G72" s="15" t="inlineStr">
@@ -5890,44 +5890,44 @@
       </c>
       <c r="I72" s="15" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="J72" s="15" t="n">
         <v>3</v>
       </c>
       <c r="K72" s="15" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32837</t>
+          <t>PDMDEP-32772</t>
         </is>
       </c>
       <c r="M72" s="15" t="inlineStr">
         <is>
-          <t>00164275</t>
+          <t>00163806</t>
         </is>
       </c>
       <c r="N72" s="16" t="n">
-        <v>900</v>
-      </c>
-      <c r="O72" s="17" t="n">
-        <v>0</v>
+        <v>705</v>
+      </c>
+      <c r="O72" s="16" t="n">
+        <v>1410</v>
       </c>
       <c r="P72" s="16" t="n">
-        <v>0</v>
+        <v>245.22</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32768</t>
+          <t>PDMDEP-32759</t>
         </is>
       </c>
       <c r="B73" s="12" t="inlineStr">
         <is>
-          <t>[VILLE DE REIMS] - MV app/ infra + màj carto - ON prem</t>
+          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE REIMS</t>
+          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
         </is>
       </c>
       <c r="E73" s="12" t="inlineStr">
@@ -5969,57 +5969,57 @@
         <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L73" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32772</t>
+          <t>PDMDEP-32763</t>
         </is>
       </c>
       <c r="M73" s="12" t="inlineStr">
         <is>
-          <t>00163806</t>
+          <t>00163805</t>
         </is>
       </c>
       <c r="N73" s="13" t="n">
-        <v>705</v>
+        <v>564</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>1410</v>
+        <v>940</v>
       </c>
       <c r="P73" s="13" t="n">
-        <v>245.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32759</t>
+          <t>PDMDEP-32732</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNAUTE URBAINE DU GRAND REIMS - DSIT] - MV app/ infra + màj carto</t>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>COMMUNAUTE URBAINE DU GRAND REIMS - DSIT</t>
+          <t>MAIRIE DE LA SENTINELLE</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>MV app/ infra + màj carto</t>
+          <t>Acquisition Geodp Caisse</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6029,7 +6029,7 @@
       </c>
       <c r="H74" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
@@ -6041,37 +6041,37 @@
         <v>3</v>
       </c>
       <c r="K74" s="15" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L74" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32763</t>
+          <t>PDMDEP-32741</t>
         </is>
       </c>
       <c r="M74" s="15" t="inlineStr">
         <is>
-          <t>00163805</t>
+          <t>00163789</t>
         </is>
       </c>
       <c r="N74" s="16" t="n">
-        <v>564</v>
-      </c>
-      <c r="O74" s="16" t="n">
-        <v>940</v>
+        <v>2138.2</v>
+      </c>
+      <c r="O74" s="17" t="n">
+        <v>1375.2</v>
       </c>
       <c r="P74" s="16" t="n">
-        <v>0</v>
+        <v>229.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B75" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
@@ -6081,12 +6081,12 @@
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -6101,49 +6101,49 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I75" s="12" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="J75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L75" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32741</t>
+          <t>PDMDEP-32712</t>
         </is>
       </c>
       <c r="M75" s="12" t="inlineStr">
         <is>
-          <t>00163789</t>
+          <t>00163498</t>
         </is>
       </c>
       <c r="N75" s="13" t="n">
-        <v>2138.2</v>
+        <v>283.5</v>
       </c>
       <c r="O75" s="17" t="n">
-        <v>1375.2</v>
+        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
-        <v>229.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32663</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -6153,12 +6153,12 @@
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>COMMUNE DE LA GARDE</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">MIGRATION PLACIER SIMPLE + PAX </t>
+          <t>Migration Placier</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="J76" s="15" t="n">
@@ -6189,19 +6189,19 @@
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32712</t>
+          <t>PDMDEP-32669</t>
         </is>
       </c>
       <c r="M76" s="15" t="inlineStr">
         <is>
-          <t>00163498</t>
+          <t>00163456</t>
         </is>
       </c>
       <c r="N76" s="16" t="n">
-        <v>283.5</v>
-      </c>
-      <c r="O76" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O76" s="16" t="n">
+        <v>373.5</v>
       </c>
       <c r="P76" s="16" t="n">
         <v>0</v>
@@ -6210,32 +6210,32 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32663</t>
+          <t>PDMDEP-32625</t>
         </is>
       </c>
       <c r="B77" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LA GARDE] - Migration Placier</t>
+          <t>[ANTIBES] - Modélisation LiEx</t>
         </is>
       </c>
       <c r="C77" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA GARDE</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E77" s="12" t="inlineStr">
         <is>
-          <t>Migration Placier</t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6245,69 +6245,69 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I77" s="12" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="J77" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32669</t>
+          <t>PDMDEP-32629</t>
         </is>
       </c>
       <c r="M77" s="12" t="inlineStr">
         <is>
-          <t>00163456</t>
+          <t>00163182</t>
         </is>
       </c>
       <c r="N77" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>373.5</v>
+        <v>109.68</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>0</v>
+        <v>33.75</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32625</t>
+          <t>PDMDEP-32598</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Modélisation LiEx</t>
+          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ANTIBES</t>
+          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Déploiement GeoDP Caisse</t>
         </is>
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -6317,7 +6317,7 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
@@ -6329,57 +6329,57 @@
         <v>3</v>
       </c>
       <c r="K78" s="15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="L78" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32629</t>
+          <t>PDMDEP-32607</t>
         </is>
       </c>
       <c r="M78" s="15" t="inlineStr">
         <is>
-          <t>00163182</t>
+          <t>00163155</t>
         </is>
       </c>
       <c r="N78" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O78" s="16" t="n">
-        <v>109.68</v>
+        <v>552</v>
+      </c>
+      <c r="O78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P78" s="16" t="n">
-        <v>33.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32598</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B79" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MOLLANS SUR OUVEZE] - Déploiement GeoDP Caisse</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="C79" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MOLLANS SUR OUVEZE</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="E79" s="12" t="inlineStr">
         <is>
-          <t>Déploiement GeoDP Caisse</t>
+          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6389,69 +6389,69 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I79" s="12" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>01/04/2026</t>
         </is>
       </c>
       <c r="J79" s="12" t="n">
         <v>3</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L79" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32607</t>
+          <t>PDMDEP-32556</t>
         </is>
       </c>
       <c r="M79" s="12" t="inlineStr">
         <is>
-          <t>00163155</t>
+          <t>00162313</t>
         </is>
       </c>
       <c r="N79" s="13" t="n">
-        <v>552</v>
-      </c>
-      <c r="O79" s="17" t="n">
-        <v>0</v>
+        <v>142.1</v>
+      </c>
+      <c r="O79" s="13" t="n">
+        <v>142.1</v>
       </c>
       <c r="P79" s="13" t="n">
-        <v>0</v>
+        <v>142.1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-32461</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>NANTES METROPOLE - VDC</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Littéralis - Intégration et paramétrage des redevances d'occupation du domaine public</t>
+          <t>Migration GEODP 1 vers GEODP 2</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -6461,69 +6461,69 @@
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="J80" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K80" s="15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L80" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32556</t>
+          <t>PDMDEP-32470</t>
         </is>
       </c>
       <c r="M80" s="15" t="inlineStr">
         <is>
-          <t>00162313</t>
+          <t>00161950</t>
         </is>
       </c>
       <c r="N80" s="16" t="n">
-        <v>142.1</v>
-      </c>
-      <c r="O80" s="16" t="n">
-        <v>142.1</v>
+        <v>1868</v>
+      </c>
+      <c r="O80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P80" s="16" t="n">
-        <v>142.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32461</t>
+          <t>PDMDEP-32442</t>
         </is>
       </c>
       <c r="B81" s="12" t="inlineStr">
         <is>
-          <t>[NANTES METROPOLE - VDC] - Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="C81" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D81" s="12" t="inlineStr">
         <is>
-          <t>NANTES METROPOLE - VDC</t>
+          <t>COMMUNE DE CHAMBERY</t>
         </is>
       </c>
       <c r="E81" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP 1 vers GEODP 2</t>
+          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6533,64 +6533,64 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I81" s="12" t="inlineStr">
         <is>
-          <t>30/03/2026</t>
+          <t>27/03/2026</t>
         </is>
       </c>
       <c r="J81" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>0.25</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32470</t>
+          <t>PDMDEP-32446</t>
         </is>
       </c>
       <c r="M81" s="12" t="inlineStr">
         <is>
-          <t>00161950</t>
+          <t>00161842</t>
         </is>
       </c>
       <c r="N81" s="13" t="n">
-        <v>1868</v>
-      </c>
-      <c r="O81" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O81" s="13" t="n">
+        <v>882.5</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>0</v>
+        <v>3530</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32442</t>
+          <t>PDMDEP-32400</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHAMBERY] - Montée de version LiEx Test et prod </t>
+          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHAMBERY</t>
+          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Montée de version LiEx Test et prod </t>
+          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
@@ -6610,64 +6610,64 @@
       </c>
       <c r="I82" s="15" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="J82" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K82" s="15" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32446</t>
+          <t>PDMDEP-32406</t>
         </is>
       </c>
       <c r="M82" s="15" t="inlineStr">
         <is>
-          <t>00161842</t>
+          <t>00161680</t>
         </is>
       </c>
       <c r="N82" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="16" t="n">
-        <v>882.5</v>
+        <v>450</v>
       </c>
       <c r="P82" s="16" t="n">
-        <v>3530</v>
+        <v>360</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32400</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B83" s="12" t="inlineStr">
         <is>
-          <t>[SM GESTION DES ROUTES DE GUADELOUPE] - Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C83" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
         <is>
-          <t>SM GESTION DES ROUTES DE GUADELOUPE</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="E83" s="12" t="inlineStr">
         <is>
-          <t>Littéralis Expert - Interface Parapheur Ixbus</t>
+          <t xml:space="preserve">Migration GEODP Placier </t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6677,35 +6677,35 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I83" s="12" t="inlineStr">
         <is>
-          <t>26/03/2026</t>
+          <t>25/03/2026</t>
         </is>
       </c>
       <c r="J83" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32406</t>
+          <t>PDMDEP-32340</t>
         </is>
       </c>
       <c r="M83" s="12" t="inlineStr">
         <is>
-          <t>00161680</t>
+          <t>00161493</t>
         </is>
       </c>
       <c r="N83" s="13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="P83" s="13" t="n">
         <v>0</v>
@@ -6714,32 +6714,32 @@
     <row r="84">
       <c r="A84" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-32264</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>CA DU NIORTAIS</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP Placier </t>
+          <t>Modélisation</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -6749,69 +6749,65 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>23/03/2026</t>
         </is>
       </c>
       <c r="J84" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32340</t>
+          <t>PDMDEP-32268</t>
         </is>
       </c>
       <c r="M84" s="15" t="inlineStr">
         <is>
-          <t>00161493</t>
+          <t>00161073</t>
         </is>
       </c>
       <c r="N84" s="16" t="n">
-        <v>450</v>
-      </c>
-      <c r="O84" s="16" t="n">
-        <v>450</v>
+        <v>1046.5</v>
+      </c>
+      <c r="O84" s="17" t="n">
+        <v>637</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>0</v>
+        <v>74.94</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32264</t>
+          <t>PDMDEP-32152</t>
         </is>
       </c>
       <c r="B85" s="12" t="inlineStr">
         <is>
-          <t>[CA DU NIORTAIS] - Modélisation 5j</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>Remy VINCENT</t>
-        </is>
-      </c>
+          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr"/>
       <c r="D85" s="12" t="inlineStr">
         <is>
-          <t>CA DU NIORTAIS</t>
+          <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
       <c r="E85" s="12" t="inlineStr">
         <is>
-          <t>Modélisation</t>
+          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
       <c r="F85" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6821,60 +6817,64 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I85" s="12" t="inlineStr">
         <is>
-          <t>23/03/2026</t>
+          <t>18/03/2026</t>
         </is>
       </c>
       <c r="J85" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>8.5</v>
+        <v>4.75</v>
       </c>
       <c r="L85" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32268</t>
+          <t>PDMDEP-32161</t>
         </is>
       </c>
       <c r="M85" s="12" t="inlineStr">
         <is>
-          <t>00161073</t>
+          <t>00160661</t>
         </is>
       </c>
       <c r="N85" s="13" t="n">
-        <v>1046.5</v>
-      </c>
-      <c r="O85" s="17" t="n">
-        <v>637</v>
+        <v>765</v>
+      </c>
+      <c r="O85" s="13" t="n">
+        <v>892.5</v>
       </c>
       <c r="P85" s="13" t="n">
-        <v>74.94</v>
+        <v>187.89</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32152</t>
+          <t>PDMDEP-32121</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
-        </is>
-      </c>
-      <c r="C86" s="15" t="inlineStr"/>
+          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+        </is>
+      </c>
+      <c r="C86" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAVAILLON</t>
+          <t>COMMUNE DE SARAN</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
+          <t>Migration GEODP TLPE + Exp Ciril</t>
         </is>
       </c>
       <c r="F86" s="15" t="inlineStr">
@@ -6901,52 +6901,52 @@
         <v>4</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>4.75</v>
+        <v>1.25</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32161</t>
+          <t>PDMDEP-32128</t>
         </is>
       </c>
       <c r="M86" s="15" t="inlineStr">
         <is>
-          <t>00160661</t>
+          <t>00160621</t>
         </is>
       </c>
       <c r="N86" s="16" t="n">
-        <v>765</v>
+        <v>0</v>
       </c>
       <c r="O86" s="16" t="n">
-        <v>892.5</v>
+        <v>300</v>
       </c>
       <c r="P86" s="16" t="n">
-        <v>187.89</v>
+        <v>240</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32121</t>
+          <t>PDMDEP-32086</t>
         </is>
       </c>
       <c r="B87" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARAN] - Migration GEODP TLPE + Exp Ciril</t>
+          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARAN</t>
+          <t>COMMUNE DE VITRY LE FRANCOIS</t>
         </is>
       </c>
       <c r="E87" s="12" t="inlineStr">
         <is>
-          <t>Migration GEODP TLPE + Exp Ciril</t>
+          <t>Acquisition Geodp Placier</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -6961,49 +6961,49 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I87" s="12" t="inlineStr">
         <is>
-          <t>18/03/2026</t>
+          <t>17/03/2026</t>
         </is>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L87" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32128</t>
+          <t>PDMDEP-32095</t>
         </is>
       </c>
       <c r="M87" s="12" t="inlineStr">
         <is>
-          <t>00160621</t>
+          <t>00160474</t>
         </is>
       </c>
       <c r="N87" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O87" s="13" t="n">
-        <v>300</v>
+        <v>407</v>
+      </c>
+      <c r="O87" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P87" s="13" t="n">
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32086</t>
+          <t>PDMDEP-32065</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE VITRY LE FRANCOIS] - Acquisition Geodp Placier</t>
+          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY LE FRANCOIS</t>
+          <t>COMMUNE DE MONTBRISON</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Placier</t>
+          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
         </is>
       </c>
       <c r="F88" s="15" t="inlineStr">
@@ -7033,32 +7033,32 @@
       </c>
       <c r="H88" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
         <is>
-          <t>17/03/2026</t>
+          <t>16/03/2026</t>
         </is>
       </c>
       <c r="J88" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K88" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32095</t>
+          <t>PDMDEP-32074</t>
         </is>
       </c>
       <c r="M88" s="15" t="inlineStr">
         <is>
-          <t>00160474</t>
+          <t>00160409</t>
         </is>
       </c>
       <c r="N88" s="16" t="n">
-        <v>407</v>
+        <v>257.15</v>
       </c>
       <c r="O88" s="17" t="n">
         <v>0</v>
@@ -7070,32 +7070,32 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32065</t>
+          <t>PDMDEP-32039</t>
         </is>
       </c>
       <c r="B89" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTBRISON] - Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTBRISON</t>
+          <t>Commune de la Croix Valmer</t>
         </is>
       </c>
       <c r="E89" s="12" t="inlineStr">
         <is>
-          <t>Migration GeODP Placier + Ajout Civil Net Finance</t>
+          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7105,32 +7105,32 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I89" s="12" t="inlineStr">
         <is>
-          <t>16/03/2026</t>
+          <t>13/03/2026</t>
         </is>
       </c>
       <c r="J89" s="12" t="n">
         <v>4</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>0.25</v>
+        <v>2.25</v>
       </c>
       <c r="L89" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32074</t>
+          <t>PDMDEP-32046</t>
         </is>
       </c>
       <c r="M89" s="12" t="inlineStr">
         <is>
-          <t>00160409</t>
+          <t>00160148</t>
         </is>
       </c>
       <c r="N89" s="13" t="n">
-        <v>257.15</v>
+        <v>440.38</v>
       </c>
       <c r="O89" s="17" t="n">
         <v>0</v>
@@ -7142,32 +7142,32 @@
     <row r="90">
       <c r="A90" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-32039</t>
+          <t>PDMDEP-31996</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de la Croix Valmer] - Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>Commune de la Croix Valmer</t>
+          <t>Commune de Cluny</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Littéralis Expert / DA DPA / Verif </t>
+          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -7177,32 +7177,32 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>13/03/2026</t>
+          <t>12/03/2026</t>
         </is>
       </c>
       <c r="J90" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K90" s="15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32046</t>
+          <t>PDMDEP-32002</t>
         </is>
       </c>
       <c r="M90" s="15" t="inlineStr">
         <is>
-          <t>00160148</t>
+          <t>00160078</t>
         </is>
       </c>
       <c r="N90" s="16" t="n">
-        <v>440.38</v>
+        <v>285</v>
       </c>
       <c r="O90" s="17" t="n">
         <v>0</v>
@@ -7214,32 +7214,32 @@
     <row r="91">
       <c r="A91" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31996</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Commune de Cluny] - Ajout d'un module caisse + Paiement cb </t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Commune de Cluny</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="E91" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout d'un module caisse + Paiement cb </t>
+          <t>SSO/LDAP</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="I91" s="12" t="inlineStr">
         <is>
-          <t>12/03/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J91" s="12" t="n">
@@ -7265,19 +7265,19 @@
       </c>
       <c r="L91" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32002</t>
+          <t>PDMDEP-31951</t>
         </is>
       </c>
       <c r="M91" s="12" t="inlineStr">
         <is>
-          <t>00160078</t>
+          <t>00159724</t>
         </is>
       </c>
       <c r="N91" s="13" t="n">
-        <v>285</v>
-      </c>
-      <c r="O91" s="17" t="n">
-        <v>0</v>
+        <v>120</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>120</v>
       </c>
       <c r="P91" s="13" t="n">
         <v>0</v>
@@ -7286,32 +7286,32 @@
     <row r="92">
       <c r="A92" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
         <is>
-          <t>SSO/LDAP</t>
+          <t>GeODP tous modules - intégration en masse n° tiers</t>
         </is>
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -7337,19 +7337,19 @@
       </c>
       <c r="L92" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31951</t>
+          <t>PDMDEP-31942</t>
         </is>
       </c>
       <c r="M92" s="15" t="inlineStr">
         <is>
-          <t>00159724</t>
+          <t>00159717</t>
         </is>
       </c>
       <c r="N92" s="16" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="O92" s="16" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="P92" s="16" t="n">
         <v>0</v>
@@ -7358,27 +7358,27 @@
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-31908</t>
         </is>
       </c>
       <c r="B93" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- GeODP tous modules - intégration en masse n° tiers</t>
+          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>Commune de GUINGAMP</t>
         </is>
       </c>
       <c r="E93" s="12" t="inlineStr">
         <is>
-          <t>GeODP tous modules - intégration en masse n° tiers</t>
+          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I93" s="12" t="inlineStr">
@@ -7409,19 +7409,19 @@
       </c>
       <c r="L93" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31942</t>
+          <t>PDMDEP-31917</t>
         </is>
       </c>
       <c r="M93" s="12" t="inlineStr">
         <is>
-          <t>00159717</t>
+          <t>00159608</t>
         </is>
       </c>
       <c r="N93" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O93" s="13" t="n">
-        <v>45</v>
+        <v>367.5</v>
       </c>
       <c r="P93" s="13" t="n">
         <v>0</v>
@@ -7430,12 +7430,12 @@
     <row r="94">
       <c r="A94" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31908</t>
+          <t>PDMDEP-31812</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
         <is>
-          <t>[Commune de GUINGAMP] - Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Commune de GUINGAMP</t>
+          <t>COMMUNE PROVINS</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>Migration GEODP Placier 2 + Ajout du paiement CB + Acquisition du TPE PAX A920</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
@@ -7470,59 +7470,59 @@
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>06/03/2026</t>
         </is>
       </c>
       <c r="J94" s="15" t="n">
         <v>4</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31917</t>
+          <t>PDMDEP-31821</t>
         </is>
       </c>
       <c r="M94" s="15" t="inlineStr">
         <is>
-          <t>00159608</t>
+          <t>00159471</t>
         </is>
       </c>
       <c r="N94" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="O94" s="16" t="n">
-        <v>367.5</v>
+        <v>420</v>
       </c>
       <c r="P94" s="16" t="n">
-        <v>0</v>
+        <v>420</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31812</t>
+          <t>PDMDEP-31649</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE PROVINS] - Migration V2 classique</t>
+          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE PROVINS</t>
+          <t>MAIRIE DE GUILLESTRE</t>
         </is>
       </c>
       <c r="E95" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>GeoDP Placier</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -7537,49 +7537,49 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I95" s="12" t="inlineStr">
         <is>
-          <t>06/03/2026</t>
+          <t>27/02/2026</t>
         </is>
       </c>
       <c r="J95" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K95" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L95" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31821</t>
+          <t>PDMDEP-31658</t>
         </is>
       </c>
       <c r="M95" s="12" t="inlineStr">
         <is>
-          <t>00159471</t>
+          <t>00158175</t>
         </is>
       </c>
       <c r="N95" s="13" t="n">
-        <v>420</v>
-      </c>
-      <c r="O95" s="13" t="n">
-        <v>420</v>
+        <v>203.5</v>
+      </c>
+      <c r="O95" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P95" s="13" t="n">
-        <v>420</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31649</t>
+          <t>PDMDEP-31589</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE GUILLESTRE] - GeoDP Placier</t>
+          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE GUILLESTRE</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>GeoDP Placier</t>
+          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
         </is>
       </c>
       <c r="F96" s="15" t="inlineStr">
@@ -7609,34 +7609,34 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>27/02/2026</t>
+          <t>26/02/2026</t>
         </is>
       </c>
       <c r="J96" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K96" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L96" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31658</t>
+          <t>PDMDEP-31596</t>
         </is>
       </c>
       <c r="M96" s="15" t="inlineStr">
         <is>
-          <t>00158175</t>
+          <t>00157967</t>
         </is>
       </c>
       <c r="N96" s="16" t="n">
-        <v>203.5</v>
-      </c>
-      <c r="O96" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P96" s="16" t="n">
@@ -7646,32 +7646,32 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31589</t>
+          <t>PDMDEP-31540</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE LEVALLOIS PERRET] - Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>COMMUNE DE MONTELIMAR</t>
         </is>
       </c>
       <c r="E97" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Migration GEODP - 3 MODULES + mise en service export finance </t>
+          <t>Modélisation LiEx</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -7681,64 +7681,64 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I97" s="12" t="inlineStr">
         <is>
-          <t>26/02/2026</t>
+          <t>24/02/2026</t>
         </is>
       </c>
       <c r="J97" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31596</t>
+          <t>PDMDEP-31546</t>
         </is>
       </c>
       <c r="M97" s="12" t="inlineStr">
         <is>
-          <t>00157967</t>
+          <t>00157816</t>
         </is>
       </c>
       <c r="N97" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O97" s="13" t="n">
-        <v>0</v>
+        <v>1500</v>
+      </c>
+      <c r="O97" s="17" t="n">
+        <v>322.35</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>0</v>
+        <v>128.94</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31540</t>
+          <t>PDMDEP-31516</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE MONTELIMAR] - Modélisation LiEx et redevances</t>
+          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE MONTELIMAR</t>
+          <t>COMMUNE DE VIRE NORMANDIE</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Modélisation LiEx</t>
+          <t>Litteralis Verif</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
@@ -7765,82 +7765,82 @@
         <v>5</v>
       </c>
       <c r="K98" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L98" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-31546</t>
-        </is>
-      </c>
-      <c r="M98" s="15" t="inlineStr">
-        <is>
-          <t>00157816</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L98" s="15" t="inlineStr"/>
+      <c r="M98" s="15" t="inlineStr"/>
       <c r="N98" s="16" t="n">
-        <v>1500</v>
-      </c>
-      <c r="O98" s="17" t="n">
-        <v>322.35</v>
+        <v>0</v>
+      </c>
+      <c r="O98" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P98" s="16" t="n">
-        <v>128.94</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31516</t>
+          <t>PDMDEP-31479</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>[VIRE NORMANDIE] - Litteralis Verif</t>
+          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE VIRE NORMANDIE</t>
+          <t>COMMUNE DE TREGUIER</t>
         </is>
       </c>
       <c r="E99" s="12" t="inlineStr">
         <is>
-          <t>Litteralis Verif</t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I99" s="12" t="inlineStr">
         <is>
-          <t>24/02/2026</t>
+          <t>20/02/2026</t>
         </is>
       </c>
       <c r="J99" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K99" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L99" s="12" t="inlineStr"/>
-      <c r="M99" s="12" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="L99" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-31488</t>
+        </is>
+      </c>
+      <c r="M99" s="12" t="inlineStr">
+        <is>
+          <t>00157472</t>
+        </is>
+      </c>
       <c r="N99" s="13" t="n">
         <v>0</v>
       </c>
@@ -7854,32 +7854,32 @@
     <row r="100">
       <c r="A100" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31479</t>
+          <t>PDMDEP-31464</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE TREGUIER] - Migration vers GeoDP V2 [RETOUR COMMERCE SANS REPONSE DU CLIENT]</t>
+          <t>[CD 17] - Modélisation PV - 2 jours</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE TREGUIER</t>
+          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G100" s="15" t="inlineStr">
@@ -7889,28 +7889,28 @@
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>20/02/2026</t>
+          <t>19/02/2026</t>
         </is>
       </c>
       <c r="J100" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K100" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L100" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31488</t>
+          <t>PDMDEP-31468</t>
         </is>
       </c>
       <c r="M100" s="15" t="inlineStr">
         <is>
-          <t>00157472</t>
+          <t>00157346</t>
         </is>
       </c>
       <c r="N100" s="16" t="n">
@@ -7926,32 +7926,32 @@
     <row r="101">
       <c r="A101" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31464</t>
+          <t>PDMDEP-31351</t>
         </is>
       </c>
       <c r="B101" s="12" t="inlineStr">
         <is>
-          <t>[CD 17] - Modélisation PV - 2 jours</t>
+          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA CHARENTE MARITIME (CD 17)</t>
+          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
         </is>
       </c>
       <c r="E101" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 jours de modélisation - nouveau modèle </t>
+          <t>Migration vers GeoDP V2</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7961,34 +7961,34 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I101" s="12" t="inlineStr">
         <is>
-          <t>19/02/2026</t>
+          <t>17/02/2026</t>
         </is>
       </c>
       <c r="J101" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K101" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31468</t>
+          <t>PDMDEP-31360</t>
         </is>
       </c>
       <c r="M101" s="12" t="inlineStr">
         <is>
-          <t>00157346</t>
+          <t>00157041</t>
         </is>
       </c>
       <c r="N101" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O101" s="13" t="n">
+        <v>210</v>
+      </c>
+      <c r="O101" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P101" s="13" t="n">
@@ -7998,27 +7998,27 @@
     <row r="102">
       <c r="A102" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31351</t>
+          <t>PDMDEP-31340</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LAISSAC-SEVERAC L'EGLISE] - Migration vers GeoDP V2</t>
+          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Flavie BARDIN</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LAISSAC-SEVERAC L'EGLISE</t>
+          <t>COMMUNE DE DINARD</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Migration vers GeoDP V2</t>
+          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -8045,22 +8045,22 @@
         <v>5</v>
       </c>
       <c r="K102" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L102" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31360</t>
+          <t>PDMDEP-31346</t>
         </is>
       </c>
       <c r="M102" s="15" t="inlineStr">
         <is>
-          <t>00157041</t>
+          <t>00157037</t>
         </is>
       </c>
       <c r="N102" s="16" t="n">
-        <v>210</v>
-      </c>
-      <c r="O102" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O102" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P102" s="16" t="n">
@@ -8070,32 +8070,32 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31340</t>
+          <t>PDMDEP-31269</t>
         </is>
       </c>
       <c r="B103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE DINARD] - Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>[DIJON METROPOLE] - Crédit d'heures</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Flavie BARDIN</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE DINARD</t>
+          <t>DIJON METROPOLE</t>
         </is>
       </c>
       <c r="E103" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ajout module caisse parking / Ajout export finance pour module placier </t>
+          <t>Crédit d'heures</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -8110,64 +8110,64 @@
       </c>
       <c r="I103" s="12" t="inlineStr">
         <is>
-          <t>17/02/2026</t>
+          <t>13/02/2026</t>
         </is>
       </c>
       <c r="J103" s="12" t="n">
         <v>5</v>
       </c>
       <c r="K103" s="12" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L103" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31346</t>
+          <t>PDMDEP-31273</t>
         </is>
       </c>
       <c r="M103" s="12" t="inlineStr">
         <is>
-          <t>00157037</t>
+          <t>0000ENATTENTEVRAIBDC</t>
         </is>
       </c>
       <c r="N103" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O103" s="13" t="n">
-        <v>0</v>
+        <v>28.1</v>
       </c>
       <c r="P103" s="13" t="n">
-        <v>0</v>
+        <v>18.73</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31269</t>
+          <t>PDMDEP-31188</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
         <is>
-          <t>[DIJON METROPOLE] - Crédit d'heures</t>
+          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>DIJON METROPOLE</t>
+          <t>COMMUNE D HENDAYE</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Crédit d'heures</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
@@ -8177,49 +8177,49 @@
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>13/02/2026</t>
+          <t>12/02/2026</t>
         </is>
       </c>
       <c r="J104" s="15" t="n">
         <v>5</v>
       </c>
       <c r="K104" s="15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31273</t>
+          <t>PDMDEP-31197</t>
         </is>
       </c>
       <c r="M104" s="15" t="inlineStr">
         <is>
-          <t>0000ENATTENTEVRAIBDC</t>
+          <t>00156556</t>
         </is>
       </c>
       <c r="N104" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O104" s="16" t="n">
-        <v>28.1</v>
+        <v>130</v>
+      </c>
+      <c r="O104" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P104" s="16" t="n">
-        <v>18.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-31188</t>
+          <t>PDMDEP-31036</t>
         </is>
       </c>
       <c r="B105" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D HENDAYE] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
@@ -8229,12 +8229,12 @@
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D HENDAYE</t>
+          <t>COMMUNE DE SARLAT LA CANEDA</t>
         </is>
       </c>
       <c r="E105" s="12" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>Migration V2 classique + abo CB</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -8254,7 +8254,7 @@
       </c>
       <c r="I105" s="12" t="inlineStr">
         <is>
-          <t>12/02/2026</t>
+          <t>10/02/2026</t>
         </is>
       </c>
       <c r="J105" s="12" t="n">
@@ -8265,16 +8265,16 @@
       </c>
       <c r="L105" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31197</t>
+          <t>PDMDEP-31045</t>
         </is>
       </c>
       <c r="M105" s="12" t="inlineStr">
         <is>
-          <t>00156556</t>
+          <t>00156095</t>
         </is>
       </c>
       <c r="N105" s="13" t="n">
-        <v>130</v>
+        <v>255</v>
       </c>
       <c r="O105" s="17" t="n">
         <v>0</v>
@@ -8286,12 +8286,12 @@
     <row r="106">
       <c r="A106" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-31036</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE SARLAT LA CANEDA] - Migration V2 classique + abo CB</t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="D106" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE SARLAT LA CANEDA</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Migration V2 classique + abo CB</t>
+          <t>Migration V2 classique</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
@@ -8326,27 +8326,27 @@
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>10/02/2026</t>
+          <t>29/01/2026</t>
         </is>
       </c>
       <c r="J106" s="15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K106" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31045</t>
+          <t>PDMDEP-30366</t>
         </is>
       </c>
       <c r="M106" s="15" t="inlineStr">
         <is>
-          <t>00156095</t>
+          <t>00154569</t>
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>255</v>
+        <v>1000</v>
       </c>
       <c r="O106" s="17" t="n">
         <v>0</v>
@@ -8358,12 +8358,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30358</t>
+          <t>PDMDEP-30330</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
+          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARGELES-SUR-MER</t>
+          <t>COMMUNE DE ALENCON</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 classique</t>
+          <t>Migration 1 activité GEODP2</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -8398,7 +8398,7 @@
       </c>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>29/01/2026</t>
+          <t>28/01/2026</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
@@ -8409,16 +8409,16 @@
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30366</t>
+          <t>PDMDEP-30335</t>
         </is>
       </c>
       <c r="M107" s="12" t="inlineStr">
         <is>
-          <t>00154569</t>
+          <t>00154411</t>
         </is>
       </c>
       <c r="N107" s="13" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="O107" s="17" t="n">
         <v>0</v>
@@ -8430,27 +8430,27 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30330</t>
+          <t>PDMDEP-30311</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE ALENCON] - Migration 1 activité GEODP2</t>
+          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE ALENCON</t>
+          <t>COMMUNE DE CAEN</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Migration 1 activité GEODP2</t>
+          <t>GeODP - Modification des marges via activation Editique</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
@@ -8470,7 +8470,7 @@
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>28/01/2026</t>
+          <t>27/01/2026</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
@@ -8481,16 +8481,16 @@
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30335</t>
+          <t>PDMDEP-30316</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00154411</t>
+          <t>00154362</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>140</v>
+        <v>200</v>
       </c>
       <c r="O108" s="17" t="n">
         <v>0</v>
@@ -8502,32 +8502,32 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30311</t>
+          <t>PDMDEP-30196</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE CAEN] - GeODP - Modification des marges via activation Editique</t>
+          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CAEN</t>
+          <t>CD56</t>
         </is>
       </c>
       <c r="E109" s="12" t="inlineStr">
         <is>
-          <t>GeODP - Modification des marges via activation Editique</t>
+          <t>Paramétrage interface Pastell</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -8537,34 +8537,34 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>27/01/2026</t>
+          <t>21/01/2026</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30316</t>
+          <t>PDMDEP-30197</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>00154362</t>
+          <t>00153939</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
-        <v>200</v>
-      </c>
-      <c r="O109" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P109" s="13" t="n">
@@ -8574,12 +8574,12 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-30196</t>
+          <t>PDMDEP-30062</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DU MORBIHAN (CD 56)] - Paramétrage interface Pastell</t>
+          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>CD56</t>
+          <t>Commune de Saint-Dizier</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
         <is>
-          <t>Paramétrage interface Pastell</t>
+          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
         </is>
       </c>
       <c r="F110" s="15" t="inlineStr">
@@ -8614,29 +8614,29 @@
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>21/01/2026</t>
+          <t>19/01/2026</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>1.25</v>
+        <v>0.75</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30197</t>
+          <t>PDMDEP-30063</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>00153939</t>
+          <t>00153633</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>350</v>
+      </c>
+      <c r="O110" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8646,27 +8646,27 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-30062</t>
+          <t>PDMDEP-29948</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[Commune de Saint-Dizier] - Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Commune de Saint-Dizier</t>
+          <t>MAIRE DE PONTARLIER</t>
         </is>
       </c>
       <c r="E111" s="12" t="inlineStr">
         <is>
-          <t>Mise en place Pack Littéralis Vision (Cartographie en ligne + Page publication dématerialisée des actes de Littéralis)</t>
+          <t>Projet d'options supplémentaires Littéralis Expert</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -8686,29 +8686,29 @@
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>19/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>0.75</v>
+        <v>8</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30063</t>
+          <t>PDMDEP-29949</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>00153633</t>
+          <t>00152726</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
-        <v>350</v>
-      </c>
-      <c r="O111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O111" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P111" s="13" t="n">
@@ -8718,32 +8718,32 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29948</t>
+          <t>PDMDEP-29685</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[PONTARLIER] - Paramétrages + Vision + DA-DPA + Pastell + Civil net</t>
+          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>MAIRE DE PONTARLIER</t>
+          <t>COMMUNE DE FREJUS</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
         <is>
-          <t>Projet d'options supplémentaires Littéralis Expert</t>
+          <t>Migration V2 ODP</t>
         </is>
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
@@ -8753,28 +8753,28 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>14/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>6</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>8</v>
+        <v>0.5</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29949</t>
+          <t>PDMDEP-29690</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>00152726</t>
+          <t>00152489</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8790,32 +8790,32 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29685</t>
+          <t>PDMDEP-29606</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS - Migration V2 ODP</t>
+          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FREJUS</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E113" s="12" t="inlineStr">
         <is>
-          <t>Migration V2 ODP</t>
+          <t>Paramétrages complémentaires + Vision</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8825,28 +8825,28 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>12/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
         <v>6</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>0.5</v>
+        <v>0.92</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29690</t>
+          <t>PDMDEP-30431</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>00152489</t>
+          <t>00154684</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30431</t>
+          <t>PDMDEP-29625</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>00154684</t>
+          <t>00145091</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29625</t>
+          <t>PDMDEP-29608</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>00145091</t>
+          <t>00152338</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
@@ -9006,32 +9006,32 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29606</t>
+          <t>PDMDEP-29208</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [BIARRITZ] - Paramétrages complémentaires + Vision</t>
+          <t>Commune de Calais - GEODP2 new</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>Commune de Calais</t>
         </is>
       </c>
       <c r="E116" s="15" t="inlineStr">
         <is>
-          <t>Paramétrages complémentaires + Vision</t>
+          <t>max</t>
         </is>
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9041,28 +9041,28 @@
       </c>
       <c r="H116" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>22/12/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>0.92</v>
+        <v>4.5</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29608</t>
+          <t>PDMDEP-29211</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>00152338</t>
+          <t>00148286</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
@@ -9078,32 +9078,30 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-29208</t>
+          <t>PDMDEP-29122</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais - GEODP2 new</t>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Commune de Calais</t>
-        </is>
-      </c>
-      <c r="E117" s="12" t="inlineStr">
-        <is>
-          <t>max</t>
-        </is>
+          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
+        </is>
+      </c>
+      <c r="E117" s="12" t="n">
+        <v/>
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9113,34 +9111,34 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>22/12/2025</t>
+          <t>19/12/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-29211</t>
+          <t>PDMDEP-29124</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00148286</t>
+          <t>00148148</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="13" t="n">
+        <v>157.5</v>
+      </c>
+      <c r="O117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P117" s="13" t="n">
@@ -9150,30 +9148,32 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-29122</t>
+          <t>PDMDEP-28306</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79) - LITTERALIS - Flux WFS communication</t>
+          <t>Commune de CLAMART - GEODP2 migration</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Maxime PONTONNIER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DES DEUX SEVRES (CD 79)</t>
-        </is>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v/>
+          <t>Commune de CLAMART</t>
+        </is>
+      </c>
+      <c r="E118" s="15" t="inlineStr">
+        <is>
+          <t>Migration V2</t>
+        </is>
       </c>
       <c r="F118" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G118" s="15" t="inlineStr">
@@ -9183,34 +9183,34 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>19/12/2025</t>
+          <t>28/11/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-29124</t>
+          <t>PDMDEP-28531</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00148148</t>
+          <t>00145374</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
-        <v>157.5</v>
-      </c>
-      <c r="O118" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O118" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P118" s="16" t="n">
@@ -9271,7 +9271,7 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28531</t>
+          <t>PDMDEP-28310</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
@@ -9283,41 +9283,39 @@
         <v>0</v>
       </c>
       <c r="O119" s="13" t="n">
-        <v>0</v>
+        <v>405</v>
       </c>
       <c r="P119" s="13" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28306</t>
+          <t>PDMDEP-28174</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART - GEODP2 migration</t>
+          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
         </is>
       </c>
       <c r="C120" s="15" t="inlineStr">
         <is>
-          <t>Maxime PONTONNIER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Commune de CLAMART</t>
-        </is>
-      </c>
-      <c r="E120" s="15" t="inlineStr">
-        <is>
-          <t>Migration V2</t>
-        </is>
+          <t>COMMUNE DE BOBIGNY</t>
+        </is>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v/>
       </c>
       <c r="F120" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G120" s="15" t="inlineStr">
@@ -9327,49 +9325,49 @@
       </c>
       <c r="H120" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>28/11/2025</t>
+          <t>25/11/2025</t>
         </is>
       </c>
       <c r="J120" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K120" s="15" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28310</t>
+          <t>PDMDEP-28175</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>00145374</t>
+          <t>00145001</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
-        <v>0</v>
+        <v>2812.32</v>
       </c>
       <c r="O120" s="16" t="n">
-        <v>405</v>
+        <v>3453.22</v>
       </c>
       <c r="P120" s="16" t="n">
-        <v>810</v>
+        <v>986.63</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-28174</t>
+          <t>PDMDEP-28095</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9379,11 +9377,13 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BOBIGNY</t>
-        </is>
-      </c>
-      <c r="E121" s="12" t="n">
-        <v/>
+          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
+        </is>
+      </c>
+      <c r="E121" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
         <is>
@@ -9402,33 +9402,33 @@
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>25/11/2025</t>
+          <t>24/11/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>3.5</v>
+        <v>1.25</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28175</t>
+          <t>PDMDEP-28206</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>00145001</t>
+          <t>00144864</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
-        <v>2812.32</v>
-      </c>
-      <c r="O121" s="13" t="n">
-        <v>3453.22</v>
+        <v>392.5</v>
+      </c>
+      <c r="O121" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P121" s="13" t="n">
-        <v>986.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -9485,16 +9485,16 @@
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28206</t>
+          <t>PDMDEP-28205</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>00144864</t>
+          <t>00144863</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
-        <v>392.5</v>
+        <v>1556.25</v>
       </c>
       <c r="O122" s="17" t="n">
         <v>0</v>
@@ -9557,22 +9557,22 @@
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28205</t>
+          <t>PDMDEP-28204</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>00144863</t>
+          <t>00144862</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
-        <v>1556.25</v>
+        <v>1790</v>
       </c>
       <c r="O123" s="17" t="n">
-        <v>0</v>
+        <v>895</v>
       </c>
       <c r="P123" s="13" t="n">
-        <v>0</v>
+        <v>716</v>
       </c>
     </row>
     <row r="124">
@@ -9629,18 +9629,18 @@
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28204</t>
+          <t>PDMDEP-28203</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>00144862</t>
+          <t>00144860</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>1790</v>
-      </c>
-      <c r="O124" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P124" s="16" t="n">
@@ -9701,12 +9701,12 @@
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28203</t>
+          <t>PDMDEP-28202</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>00144860</t>
+          <t>00144857</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
@@ -9722,12 +9722,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-28095</t>
+          <t>PDMDEP-27634</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD91) - LITTERALIS</t>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9737,13 +9737,11 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L' ESSONNE (CD 91)</t>
-        </is>
-      </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v/>
       </c>
       <c r="F126" s="15" t="inlineStr">
         <is>
@@ -9757,28 +9755,28 @@
       </c>
       <c r="H126" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>24/11/2025</t>
+          <t>21/11/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>1.25</v>
+        <v>8</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28202</t>
+          <t>PDMDEP-27642</t>
         </is>
       </c>
       <c r="M126" s="15" t="inlineStr">
         <is>
-          <t>00144857</t>
+          <t>00143935</t>
         </is>
       </c>
       <c r="N126" s="16" t="n">
@@ -9794,12 +9792,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-27634</t>
+          <t>PDMDEP-27543</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes - LITTERALIS</t>
+          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9809,7 +9807,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU VAUCLUSE (CD 84) - Direction des Routes</t>
+          <t>COMMUNE DE VITRY SUR SEINE</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9827,49 +9825,49 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>21/11/2025</t>
+          <t>20/11/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27642</t>
+          <t>PDMDEP-27557</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>00143935</t>
+          <t>00144532</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
-        <v>0</v>
+        <v>732</v>
+      </c>
+      <c r="O127" s="17" t="n">
+        <v>640</v>
       </c>
       <c r="P127" s="13" t="n">
-        <v>0</v>
+        <v>213.33</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-27543</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
@@ -9879,67 +9877,53 @@
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE VITRY SUR SEINE</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v/>
-      </c>
-      <c r="F128" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>CD74</t>
+        </is>
+      </c>
+      <c r="E128" s="15" t="inlineStr">
+        <is>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F128" s="15" t="inlineStr"/>
       <c r="G128" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>20/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27557</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>00144532</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
-        <v>732</v>
-      </c>
-      <c r="O128" s="17" t="n">
-        <v>640</v>
+        <v>0</v>
+      </c>
+      <c r="O128" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P128" s="16" t="n">
-        <v>213.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26831</t>
+          <t>PDMDEP-26825</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
+          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -9949,21 +9933,27 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>CD74</t>
-        </is>
-      </c>
-      <c r="E129" s="12" t="inlineStr">
-        <is>
-          <t>MAJ carto</t>
-        </is>
-      </c>
-      <c r="F129" s="12" t="inlineStr"/>
+          <t>VILLE DE COLOMBES</t>
+        </is>
+      </c>
+      <c r="E129" s="12" t="n">
+        <v/>
+      </c>
+      <c r="F129" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Maintenance</t>
-        </is>
-      </c>
-      <c r="H129" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H129" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
           <t>05/11/2025</t>
@@ -9973,15 +9963,23 @@
         <v>8</v>
       </c>
       <c r="K129" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L129" s="12" t="inlineStr"/>
-      <c r="M129" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L129" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-26826</t>
+        </is>
+      </c>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>00142974</t>
+        </is>
+      </c>
       <c r="N129" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O129" s="13" t="n">
-        <v>0</v>
+        <v>465</v>
       </c>
       <c r="P129" s="13" t="n">
         <v>0</v>
@@ -9990,12 +9988,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26825</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -10005,7 +10003,7 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -10028,58 +10026,60 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>05/11/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
         <v>8</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26826</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M130" s="15" t="inlineStr">
         <is>
-          <t>00142974</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O130" s="16" t="n">
-        <v>465</v>
+        <v>230</v>
       </c>
       <c r="P130" s="16" t="n">
-        <v>0</v>
+        <v>184</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26813</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
-        </is>
-      </c>
-      <c r="E131" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E131" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
@@ -10093,65 +10093,63 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>04/11/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>1.25</v>
+        <v>9.5</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26814</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>00142941</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O131" s="13" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement LiEx</t>
-        </is>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+        </is>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v/>
       </c>
       <c r="F132" s="15" t="inlineStr">
         <is>
@@ -10170,23 +10168,23 @@
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>9.5</v>
+        <v>1.5</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26783</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M132" s="15" t="inlineStr">
         <is>
-          <t>00142659</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N132" s="16" t="n">
@@ -10202,12 +10200,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
@@ -10217,7 +10215,7 @@
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10235,34 +10233,34 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>9</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O133" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O133" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10272,22 +10270,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-24598</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>COMMUNE DE LA CIOTAT - GEODP2 migration</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>COMMUNE DE LA CIOTAT</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10295,7 +10293,7 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
@@ -10305,35 +10303,35 @@
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
         <v>9</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L134" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-28061</t>
         </is>
       </c>
       <c r="M134" s="15" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>501305</t>
         </is>
       </c>
       <c r="N134" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O134" s="16" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="P134" s="16" t="n">
         <v>0</v>
@@ -10342,22 +10340,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24598</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA CIOTAT - GEODP2 migration</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LA CIOTAT</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10365,7 +10363,7 @@
       </c>
       <c r="F135" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -10375,35 +10373,35 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L135" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28061</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M135" s="12" t="inlineStr">
         <is>
-          <t>501305</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N135" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O135" s="13" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="P135" s="13" t="n">
         <v>0</v>
@@ -10412,12 +10410,12 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
@@ -10427,7 +10425,7 @@
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10445,28 +10443,28 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>0.5</v>
+        <v>3.62</v>
       </c>
       <c r="L136" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M136" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N136" s="16" t="n">
@@ -10531,12 +10529,12 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10552,22 +10550,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10590,29 +10588,29 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>3.62</v>
+        <v>5.75</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O138" s="16" t="n">
+        <v>2323</v>
+      </c>
+      <c r="O138" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
@@ -10622,22 +10620,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10645,7 +10643,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10655,35 +10653,35 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O139" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O139" s="13" t="n">
+        <v>964.1</v>
       </c>
       <c r="P139" s="13" t="n">
         <v>0</v>
@@ -10692,12 +10690,12 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10741,19 +10739,19 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O140" s="16" t="n">
-        <v>964.1</v>
+        <v>140.4</v>
       </c>
       <c r="P140" s="16" t="n">
         <v>0</v>
@@ -10762,22 +10760,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10785,7 +10783,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10795,35 +10793,35 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="13" t="n">
-        <v>140.4</v>
+        <v>0</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10832,22 +10830,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10865,28 +10863,28 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
@@ -10902,22 +10900,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10935,28 +10933,28 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2</v>
+        <v>0.19</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
@@ -11021,12 +11019,12 @@
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
@@ -11057,7 +11055,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11091,12 +11089,12 @@
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
@@ -11127,7 +11125,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11161,12 +11159,12 @@
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11182,12 +11180,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11197,7 +11195,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11215,28 +11213,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11252,22 +11250,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11290,23 +11288,23 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K148" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11322,22 +11320,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11345,7 +11343,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -11360,30 +11358,30 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="13" t="n">
-        <v>0</v>
+        <v>482.72</v>
       </c>
       <c r="P149" s="13" t="n">
         <v>0</v>
@@ -11392,22 +11390,18 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
-        </is>
-      </c>
-      <c r="C150" s="15" t="inlineStr">
-        <is>
-          <t>Alizée MARGOT</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr"/>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11415,7 +11409,7 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
@@ -11441,19 +11435,19 @@
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>482.72</v>
+        <v>575</v>
       </c>
       <c r="P150" s="16" t="n">
         <v>0</v>
@@ -11462,18 +11456,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr"/>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11491,35 +11489,35 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="P151" s="13" t="n">
         <v>0</v>
@@ -11528,22 +11526,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11561,34 +11559,34 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O152" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O152" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="16" t="n">
@@ -11598,22 +11596,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11636,54 +11634,54 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="O153" s="17" t="n">
-        <v>0</v>
+        <v>230</v>
+      </c>
+      <c r="O153" s="13" t="n">
+        <v>230</v>
       </c>
       <c r="P153" s="13" t="n">
-        <v>0</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-20217</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>CAP ATLANTIQUE</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11691,7 +11689,7 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
@@ -11706,54 +11704,54 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28028</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>464365</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="O154" s="16" t="n">
-        <v>230</v>
+        <v>660</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>102.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20217</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CAP ATLANTIQUE</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11761,7 +11759,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11769,37 +11767,25 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H155" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H155" s="12" t="inlineStr"/>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28028</t>
-        </is>
-      </c>
-      <c r="M155" s="12" t="inlineStr">
-        <is>
-          <t>464365</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr"/>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="13" t="n">
-        <v>660</v>
+        <v>0</v>
       </c>
       <c r="P155" s="13" t="n">
         <v>0</v>
@@ -11808,22 +11794,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11839,20 +11825,32 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H156" s="15" t="inlineStr"/>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr"/>
-      <c r="M156" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28027</t>
+        </is>
+      </c>
+      <c r="M156" s="15" t="inlineStr">
+        <is>
+          <t>470688</t>
+        </is>
+      </c>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
@@ -11866,12 +11864,12 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11881,7 +11879,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11899,28 +11897,28 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>1.5</v>
+        <v>0.25</v>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28027</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>470688</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N157" s="13" t="n">
@@ -11936,12 +11934,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11951,7 +11949,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11969,28 +11967,28 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
@@ -12006,12 +12004,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -12021,7 +12019,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -12044,23 +12042,23 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N159" s="13" t="n">
@@ -12076,12 +12074,12 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
@@ -12091,11 +12089,13 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
-        </is>
-      </c>
-      <c r="E160" s="15" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
@@ -12104,35 +12104,27 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27535</t>
-        </is>
-      </c>
-      <c r="M160" s="15" t="inlineStr">
-        <is>
-          <t>465345</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr"/>
+      <c r="M160" s="15" t="inlineStr"/>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
@@ -12146,28 +12138,26 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>CD 74 - HAUTE SAVOIE</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="n">
+        <v/>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
@@ -12186,14 +12176,14 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12210,22 +12200,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12243,7 +12233,7 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
@@ -12255,7 +12245,7 @@
         <v>19</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.75</v>
+        <v>5.25</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12272,22 +12262,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12295,7 +12285,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -12317,7 +12307,7 @@
         <v>19</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>5.25</v>
+        <v>1.5</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12334,12 +12324,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12349,7 +12339,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12362,31 +12352,39 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr"/>
-      <c r="M164" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28019</t>
+        </is>
+      </c>
+      <c r="M164" s="15" t="inlineStr">
+        <is>
+          <t>455151</t>
+        </is>
+      </c>
       <c r="N164" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O164" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O164" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P164" s="16" t="n">
@@ -12396,22 +12394,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12419,7 +12417,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -12429,34 +12427,34 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N165" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P165" s="13" t="n">
@@ -12481,7 +12479,7 @@
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12515,7 +12513,7 @@
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
@@ -12536,22 +12534,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-17117</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>NÎMES</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12574,30 +12572,30 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28005</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>448204</t>
         </is>
       </c>
       <c r="N167" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O167" s="13" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="P167" s="13" t="n">
         <v>0</v>
@@ -12606,22 +12604,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-17117</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>NÎMES</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12629,45 +12627,37 @@
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>14/10/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28005</t>
-        </is>
-      </c>
-      <c r="M168" s="15" t="inlineStr">
-        <is>
-          <t>448204</t>
-        </is>
-      </c>
+        <v>4.75</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr"/>
+      <c r="M168" s="15" t="inlineStr"/>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O168" s="16" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="P168" s="16" t="n">
         <v>0</v>
@@ -12676,22 +12666,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12699,7 +12689,7 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -12709,19 +12699,19 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>4.75</v>
+        <v>0.25</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12738,22 +12728,22 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12766,7 +12756,7 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
@@ -12776,17 +12766,25 @@
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr"/>
-      <c r="M170" s="15" t="inlineStr"/>
+        <v>2.5</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M170" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12800,12 +12798,12 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -12815,7 +12813,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12828,7 +12826,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H171" s="12" t="inlineStr">
@@ -12838,25 +12836,17 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K171" s="12" t="n">
         <v>2.5</v>
       </c>
-      <c r="L171" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M171" s="12" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+      <c r="L171" s="12" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr"/>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12870,22 +12860,22 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12908,14 +12898,14 @@
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12932,22 +12922,22 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -12970,14 +12960,14 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -12994,22 +12984,22 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E174" s="15" t="n">
@@ -13027,19 +13017,19 @@
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>1.5</v>
+        <v>8</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -13056,22 +13046,22 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E175" s="12" t="n">
@@ -13089,19 +13079,19 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13118,12 +13108,12 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
@@ -13133,7 +13123,7 @@
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E176" s="15" t="n">
@@ -13146,7 +13136,7 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr">
@@ -13156,17 +13146,25 @@
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L176" s="15" t="inlineStr"/>
-      <c r="M176" s="15" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M176" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N176" s="16" t="n">
         <v>0</v>
       </c>
@@ -13180,22 +13178,22 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E177" s="12" t="n">
@@ -13211,32 +13209,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H177" s="12" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
+      <c r="H177" s="12" t="inlineStr"/>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M177" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr"/>
       <c r="N177" s="13" t="n">
         <v>0</v>
       </c>
@@ -13250,12 +13236,12 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
@@ -13265,7 +13251,7 @@
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E178" s="15" t="n">
@@ -13278,23 +13264,35 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H178" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H178" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr"/>
-      <c r="M178" s="15" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M178" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13308,12 +13306,12 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
@@ -13323,7 +13321,7 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD79 - Deux Sèvres</t>
         </is>
       </c>
       <c r="E179" s="12" t="n">
@@ -13346,25 +13344,17 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M179" s="12" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr"/>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13378,26 +13368,28 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
-        </is>
-      </c>
-      <c r="E180" s="15" t="n">
-        <v/>
+          <t>[SM Routes de Guadeloupe]</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement de Littéralis Expert</t>
+        </is>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
@@ -13423,7 +13415,7 @@
         <v>34</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -13440,12 +13432,12 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD 14] Paramétrages</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
@@ -13455,12 +13447,12 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>Déploiement de Littéralis Expert</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -13475,7 +13467,7 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
@@ -13487,7 +13479,7 @@
         <v>34</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.5</v>
+        <v>9.5</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13504,27 +13496,23 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
-        </is>
-      </c>
-      <c r="C182" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr"/>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>MONTPELLIER MMM</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement Module AC</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
@@ -13539,19 +13527,19 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>9.5</v>
+        <v>1.75</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13568,25 +13556,21 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Module AC</t>
-        </is>
-      </c>
+          <t>MAIRIE DE MOUY</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr"/>
       <c r="F183" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13594,24 +13578,20 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H183" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr"/>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L183" s="12" t="inlineStr"/>
       <c r="M183" s="12" t="inlineStr"/>
@@ -13628,18 +13608,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13656,7 +13636,7 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
@@ -13680,18 +13660,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1310</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13708,14 +13688,14 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L185" s="12" t="inlineStr"/>
       <c r="M185" s="12" t="inlineStr"/>
@@ -13732,18 +13712,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1310</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13754,28 +13734,36 @@
       </c>
       <c r="G186" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L186" s="15" t="inlineStr"/>
-      <c r="M186" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L186" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34335</t>
+        </is>
+      </c>
+      <c r="M186" s="15" t="inlineStr">
+        <is>
+          <t>00168072</t>
+        </is>
+      </c>
       <c r="N186" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O186" s="16" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="P186" s="16" t="n">
         <v>0</v>
@@ -13784,18 +13772,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13812,50 +13800,50 @@
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34335</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M187" s="12" t="inlineStr">
         <is>
-          <t>00168072</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N187" s="13" t="n">
-        <v>0</v>
+        <v>510.6</v>
       </c>
       <c r="O187" s="13" t="n">
-        <v>150</v>
+        <v>680.8</v>
       </c>
       <c r="P187" s="13" t="n">
-        <v>0</v>
+        <v>389.03</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13872,50 +13860,50 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="L188" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-33167</t>
         </is>
       </c>
       <c r="M188" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00165437</t>
         </is>
       </c>
       <c r="N188" s="16" t="n">
-        <v>510.6</v>
+        <v>0</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>680.8</v>
+        <v>100</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>389.03</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13926,36 +13914,28 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L189" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-33167</t>
-        </is>
-      </c>
-      <c r="M189" s="12" t="inlineStr">
-        <is>
-          <t>00165437</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr"/>
+      <c r="M189" s="12" t="inlineStr"/>
       <c r="N189" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O189" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P189" s="13" t="n">
         <v>0</v>
@@ -13964,18 +13944,18 @@
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13992,14 +13972,14 @@
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L190" s="15" t="inlineStr"/>
       <c r="M190" s="15" t="inlineStr"/>
@@ -14016,18 +13996,18 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1021</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -14044,14 +14024,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -14068,18 +14048,18 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-589</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Mairie de Venelles</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>Mairie de Venelles</t>
         </is>
       </c>
       <c r="E192" s="15" t="inlineStr"/>
@@ -14096,11 +14076,11 @@
       <c r="H192" s="15" t="inlineStr"/>
       <c r="I192" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J192" s="15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K192" s="15" t="n">
         <v>0.5</v>
@@ -14118,83 +14098,31 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="11" t="inlineStr">
-        <is>
-          <t>PSC-589</t>
-        </is>
-      </c>
-      <c r="B193" s="12" t="inlineStr">
-        <is>
-          <t>Mairie de Venelles</t>
-        </is>
-      </c>
-      <c r="C193" s="12" t="inlineStr"/>
-      <c r="D193" s="12" t="inlineStr">
-        <is>
-          <t>Mairie de Venelles</t>
-        </is>
-      </c>
-      <c r="E193" s="12" t="inlineStr"/>
-      <c r="F193" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="G193" s="12" t="inlineStr">
-        <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H193" s="12" t="inlineStr"/>
-      <c r="I193" s="12" t="inlineStr">
-        <is>
-          <t>20/03/2025</t>
-        </is>
-      </c>
-      <c r="J193" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K193" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L193" s="12" t="inlineStr"/>
-      <c r="M193" s="12" t="inlineStr"/>
-      <c r="N193" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O193" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P193" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="18" t="inlineStr">
+      <c r="A193" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B194" s="18" t="inlineStr"/>
-      <c r="C194" s="18" t="inlineStr"/>
-      <c r="D194" s="18" t="inlineStr"/>
-      <c r="E194" s="18" t="inlineStr"/>
-      <c r="F194" s="18" t="inlineStr"/>
-      <c r="G194" s="18" t="inlineStr"/>
-      <c r="H194" s="18" t="inlineStr"/>
-      <c r="I194" s="18" t="inlineStr"/>
-      <c r="J194" s="18" t="inlineStr"/>
-      <c r="K194" s="18" t="inlineStr"/>
-      <c r="L194" s="18" t="inlineStr"/>
-      <c r="M194" s="18" t="inlineStr"/>
-      <c r="N194" s="19" t="n">
-        <v>63859.2</v>
-      </c>
-      <c r="O194" s="19" t="n">
-        <v>67702.265</v>
-      </c>
-      <c r="P194" s="19" t="n">
-        <v>190.57</v>
+      <c r="B193" s="18" t="inlineStr"/>
+      <c r="C193" s="18" t="inlineStr"/>
+      <c r="D193" s="18" t="inlineStr"/>
+      <c r="E193" s="18" t="inlineStr"/>
+      <c r="F193" s="18" t="inlineStr"/>
+      <c r="G193" s="18" t="inlineStr"/>
+      <c r="H193" s="18" t="inlineStr"/>
+      <c r="I193" s="18" t="inlineStr"/>
+      <c r="J193" s="18" t="inlineStr"/>
+      <c r="K193" s="18" t="inlineStr"/>
+      <c r="L193" s="18" t="inlineStr"/>
+      <c r="M193" s="18" t="inlineStr"/>
+      <c r="N193" s="19" t="n">
+        <v>61747.2</v>
+      </c>
+      <c r="O193" s="19" t="n">
+        <v>69262.265</v>
+      </c>
+      <c r="P193" s="19" t="n">
+        <v>194.41</v>
       </c>
     </row>
   </sheetData>
@@ -14388,7 +14316,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15416,7 +15343,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>203.25</v>
+        <v>204.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>36.25</v>
@@ -15425,17 +15352,17 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>245.25</v>
+        <v>246.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>455.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.0%</t>
         </is>
       </c>
     </row>
@@ -15477,7 +15404,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>133.08</v>
+        <v>134.08</v>
       </c>
     </row>
   </sheetData>
@@ -15562,16 +15489,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>382150</v>
+        <v>380590</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>131869</v>
+        <v>131204</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>250280</v>
+        <v>249385</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>158209</v>
+        <v>157314</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>22749</v>
@@ -15587,16 +15514,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>177055</v>
+        <v>175495</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>68860</v>
+        <v>68195</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>108195</v>
+        <v>107300</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>89698</v>
+        <v>88803</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>12192</v>

--- a/jira_export_2026-07-30.xlsx
+++ b/jira_export_2026-07-30.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>584 h</t>
+          <t>586 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -4406,9 +4406,9 @@
         </is>
       </c>
       <c r="N51" s="13" t="n">
-        <v>4040</v>
-      </c>
-      <c r="O51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="13" t="n">
         <v>1010</v>
       </c>
       <c r="P51" s="13" t="n">
@@ -5609,7 +5609,7 @@
         <v>3</v>
       </c>
       <c r="K68" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L68" s="15" t="inlineStr">
         <is>
@@ -6761,7 +6761,7 @@
         <v>4</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>637</v>
       </c>
       <c r="P84" s="16" t="n">
-        <v>74.94</v>
+        <v>70.78</v>
       </c>
     </row>
     <row r="85">
@@ -10595,7 +10595,7 @@
         <v>11</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
@@ -11571,7 +11571,7 @@
         <v>15</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
@@ -14116,13 +14116,13 @@
       <c r="L193" s="18" t="inlineStr"/>
       <c r="M193" s="18" t="inlineStr"/>
       <c r="N193" s="19" t="n">
-        <v>61747.2</v>
+        <v>57707.2</v>
       </c>
       <c r="O193" s="19" t="n">
         <v>69262.265</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>194.41</v>
+        <v>193.6</v>
       </c>
     </row>
   </sheetData>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>204.25</v>
+        <v>205.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>36.25</v>
@@ -15352,7 +15352,7 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>246.25</v>
+        <v>247.75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>69.5</v>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>134.08</v>
+        <v>135.08</v>
       </c>
     </row>
   </sheetData>
